--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e85c81c27d35d093/Dokumente/Webseiten/EIWG/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{D1314935-C5B3-4AE7-B730-4C7C0C7E3407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90CF7B47-791F-450C-963E-15F51F27D076}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{D1314935-C5B3-4AE7-B730-4C7C0C7E3407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAD0DFA5-AE32-4D73-90F0-1E3589E25781}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="202">
   <si>
     <t>Name</t>
   </si>
@@ -197,12 +197,6 @@
     <t>Paul Terrill</t>
   </si>
   <si>
-    <t>Nicolas Grégoire</t>
-  </si>
-  <si>
-    <t>Inserm</t>
-  </si>
-  <si>
     <t>Maria Efstathiou</t>
   </si>
   <si>
@@ -215,21 +209,9 @@
     <t>OncoEstimand</t>
   </si>
   <si>
-    <t>Christian Bressen Piper</t>
-  </si>
-  <si>
-    <t>Leo Pharma</t>
-  </si>
-  <si>
-    <t>Silvia Diaz</t>
-  </si>
-  <si>
     <t>Lilly</t>
   </si>
   <si>
-    <t xml:space="preserve">Health Economist </t>
-  </si>
-  <si>
     <t>Mette Krog Josiassen</t>
   </si>
   <si>
@@ -323,33 +305,21 @@
     <t>Sue McKendrick</t>
   </si>
   <si>
-    <t>Mark Baird</t>
-  </si>
-  <si>
     <t>Judith Anzures-Cabrera</t>
   </si>
   <si>
     <t>Roche</t>
   </si>
   <si>
-    <t>Benedicte Ricci</t>
-  </si>
-  <si>
     <t>Chien-Ju Lin</t>
   </si>
   <si>
-    <t xml:space="preserve">Kirkpatrick John </t>
-  </si>
-  <si>
     <t>Marcel Wolbers</t>
   </si>
   <si>
     <t>Qing Wang</t>
   </si>
   <si>
-    <t>Nikhil Kamath</t>
-  </si>
-  <si>
     <t>Claudia Hemmelmann</t>
   </si>
   <si>
@@ -410,9 +380,6 @@
     <t>Bilyana Dabin</t>
   </si>
   <si>
-    <t>Almut Mecke</t>
-  </si>
-  <si>
     <t>Barbara Glocker</t>
   </si>
   <si>
@@ -491,9 +458,6 @@
     <t>Bohdana Ratitch</t>
   </si>
   <si>
-    <t>Jonathan Fintzi</t>
-  </si>
-  <si>
     <t>BMS</t>
   </si>
   <si>
@@ -527,9 +491,6 @@
     <t>McMaster Univ, Canada</t>
   </si>
   <si>
-    <t>Simon Newsome</t>
-  </si>
-  <si>
     <t>Alexandra Lauer</t>
   </si>
   <si>
@@ -660,6 +621,27 @@
   </si>
   <si>
     <t>Ilse Van Dromme</t>
+  </si>
+  <si>
+    <t>Giusi Moffa</t>
+  </si>
+  <si>
+    <t>Abel Eshete</t>
+  </si>
+  <si>
+    <t>FDA</t>
+  </si>
+  <si>
+    <t>Shanti Gomatam</t>
+  </si>
+  <si>
+    <t>Ulrike Krahn</t>
+  </si>
+  <si>
+    <t>Yudong Zhao</t>
+  </si>
+  <si>
+    <t>PDD</t>
   </si>
 </sst>
 </file>
@@ -721,17 +703,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{4456F23E-6427-4F03-B890-5B15F2F65FD3}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -750,14 +740,6 @@
         <scheme val="none"/>
       </font>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -771,18 +753,14 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{650566AF-F73B-41F8-B217-CD1938D7378E}" name="Tabelle13" displayName="Tabelle13" ref="A1:Q124" totalsRowShown="0">
-  <autoFilter ref="A1:Q124" xr:uid="{650566AF-F73B-41F8-B217-CD1938D7378E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{650566AF-F73B-41F8-B217-CD1938D7378E}" name="Tabelle13" displayName="Tabelle13" ref="A1:Q119" totalsRowShown="0">
+  <autoFilter ref="A1:Q119" xr:uid="{650566AF-F73B-41F8-B217-CD1938D7378E}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{97E2A29D-B888-411A-9C63-65873C8422D6}" name="Name" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{97E2A29D-B888-411A-9C63-65873C8422D6}" name="Name" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{DF826309-7F45-4D14-88D8-48604C35E54D}" name="Company"/>
     <tableColumn id="4" xr3:uid="{44FE806B-64FC-4592-9F90-DBE6456CB90B}" name="Function"/>
-    <tableColumn id="5" xr3:uid="{A6AABD66-8F19-4EAF-A0DD-F4FAF5BB0696}" name="Lead" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{A6AABD66-8F19-4EAF-A0DD-F4FAF5BB0696}" name="Lead" dataDxfId="0"/>
     <tableColumn id="13" xr3:uid="{5A7BDB31-8DD4-45EA-B9DF-9FC82A30EB51}" name="Type"/>
     <tableColumn id="6" xr3:uid="{66CD400B-3B58-4C16-89AC-DEED83CDD2DF}" name="Contact to"/>
     <tableColumn id="7" xr3:uid="{E278C033-C1AC-41AA-B3B4-D52FDAD8BBE4}" name="Training"/>
@@ -1101,7 +1079,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q124"/>
+  <dimension ref="A1:Q119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.7265625" customWidth="1"/>
@@ -1161,13 +1139,13 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>173</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="Q1" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
@@ -1206,7 +1184,7 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
@@ -1255,7 +1233,7 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>
@@ -1295,7 +1273,7 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
@@ -1312,7 +1290,7 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s">
         <v>16</v>
@@ -1338,7 +1316,7 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
@@ -1458,10 +1436,10 @@
         <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1478,7 +1456,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1495,7 +1473,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1512,7 +1490,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1526,7 +1504,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1546,7 +1524,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -1559,11 +1537,8 @@
       <c r="E22" t="s">
         <v>17</v>
       </c>
-      <c r="P22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1571,67 +1546,70 @@
         <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>55</v>
       </c>
       <c r="B24" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" t="s">
         <v>56</v>
       </c>
-      <c r="C24" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M24" t="s">
+        <v>20</v>
+      </c>
+      <c r="N24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
         <v>16</v>
       </c>
-      <c r="D25" t="s">
-        <v>12</v>
-      </c>
       <c r="E25" t="s">
         <v>17</v>
       </c>
-      <c r="F25" t="s">
-        <v>58</v>
-      </c>
-      <c r="M25" t="s">
-        <v>20</v>
-      </c>
-      <c r="N25" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>43</v>
+      </c>
+      <c r="D26" t="s">
+        <v>22</v>
       </c>
       <c r="E26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>61</v>
       </c>
@@ -1639,106 +1617,115 @@
         <v>62</v>
       </c>
       <c r="C27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
         <v>63</v>
       </c>
-      <c r="E27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="B28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" t="s">
         <v>64</v>
       </c>
-      <c r="B28" t="s">
+      <c r="N28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>65</v>
       </c>
-      <c r="C28" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
         <v>66</v>
       </c>
-      <c r="B29" t="s">
-        <v>65</v>
-      </c>
       <c r="C29" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>67</v>
       </c>
       <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>68</v>
       </c>
-      <c r="C30" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
         <v>69</v>
       </c>
-      <c r="B31" t="s">
-        <v>166</v>
-      </c>
       <c r="C31" t="s">
         <v>16</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
       </c>
-      <c r="F31" t="s">
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>70</v>
       </c>
-      <c r="N31" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="B32" t="s">
         <v>71</v>
       </c>
-      <c r="B32" t="s">
-        <v>72</v>
-      </c>
       <c r="C32" t="s">
         <v>16</v>
       </c>
       <c r="E32" t="s">
         <v>17</v>
+      </c>
+      <c r="H32" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" t="s">
+        <v>20</v>
+      </c>
+      <c r="N32" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s">
         <v>73</v>
       </c>
-      <c r="B33" t="s">
-        <v>72</v>
-      </c>
       <c r="C33" t="s">
         <v>16</v>
       </c>
       <c r="E33" t="s">
-        <v>28</v>
-      </c>
-      <c r="L33" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
@@ -1754,45 +1741,60 @@
       <c r="E34" t="s">
         <v>17</v>
       </c>
+      <c r="I34" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>76</v>
       </c>
       <c r="B35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C35" t="s">
         <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H35" t="s">
         <v>20</v>
       </c>
-      <c r="J35" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" t="s">
-        <v>20</v>
-      </c>
-      <c r="N35" t="s">
+      <c r="L35" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" t="s">
         <v>78</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" t="s">
         <v>79</v>
       </c>
-      <c r="C36" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" t="s">
-        <v>17</v>
+      <c r="G36" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" t="s">
+        <v>20</v>
+      </c>
+      <c r="L36" t="s">
+        <v>20</v>
+      </c>
+      <c r="N36" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
@@ -1800,260 +1802,251 @@
         <v>80</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E37" t="s">
         <v>17</v>
-      </c>
-      <c r="I37" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C38" t="s">
         <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H38" t="s">
-        <v>20</v>
-      </c>
-      <c r="L38" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C39" t="s">
         <v>16</v>
       </c>
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
       <c r="E39" t="s">
-        <v>17</v>
-      </c>
-      <c r="F39" t="s">
-        <v>85</v>
-      </c>
-      <c r="G39" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J39" t="s">
-        <v>20</v>
-      </c>
-      <c r="L39" t="s">
-        <v>20</v>
-      </c>
-      <c r="N39" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s">
         <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s">
         <v>84</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E41" t="s">
         <v>17</v>
-      </c>
-      <c r="H41" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="E42" t="s">
-        <v>28</v>
-      </c>
-      <c r="J42" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C43" t="s">
         <v>16</v>
       </c>
+      <c r="D43" t="s">
+        <v>6</v>
+      </c>
       <c r="E43" t="s">
-        <v>134</v>
+        <v>17</v>
+      </c>
+      <c r="G43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" t="s">
+        <v>20</v>
+      </c>
+      <c r="N43" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B44" t="s">
         <v>90</v>
       </c>
       <c r="C44" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E44" t="s">
         <v>17</v>
+      </c>
+      <c r="G44" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C45" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>28</v>
+      </c>
+      <c r="L45" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C46" t="s">
         <v>16</v>
       </c>
-      <c r="D46" t="s">
-        <v>6</v>
-      </c>
       <c r="E46" t="s">
-        <v>17</v>
-      </c>
-      <c r="G46" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" t="s">
-        <v>20</v>
-      </c>
-      <c r="N46" t="s">
+        <v>28</v>
+      </c>
+      <c r="H46" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C47" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
         <v>28</v>
       </c>
+      <c r="L47" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C48" t="s">
         <v>16</v>
       </c>
       <c r="E48" t="s">
-        <v>17</v>
-      </c>
-      <c r="G48" t="s">
+        <v>28</v>
+      </c>
+      <c r="L48" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C49" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E49" t="s">
         <v>28</v>
       </c>
+      <c r="L49" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C50" t="s">
         <v>16</v>
       </c>
       <c r="E50" t="s">
-        <v>28</v>
-      </c>
-      <c r="L50" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" t="s">
         <v>100</v>
       </c>
-      <c r="B51" t="s">
-        <v>97</v>
-      </c>
       <c r="C51" t="s">
         <v>16</v>
       </c>
       <c r="E51" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="I51" t="s">
+        <v>20</v>
+      </c>
+      <c r="N51" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.35">
@@ -2061,16 +2054,13 @@
         <v>101</v>
       </c>
       <c r="B52" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C52" t="s">
         <v>16</v>
       </c>
       <c r="E52" t="s">
-        <v>28</v>
-      </c>
-      <c r="H52" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.35">
@@ -2078,46 +2068,55 @@
         <v>102</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C53" t="s">
         <v>16</v>
       </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
       <c r="E53" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="L53" t="s">
+        <v>20</v>
+      </c>
+      <c r="N53" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" t="s">
         <v>103</v>
       </c>
-      <c r="B54" t="s">
-        <v>97</v>
-      </c>
       <c r="C54" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E54" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="P54" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B55" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C55" t="s">
         <v>16</v>
       </c>
       <c r="E55" t="s">
-        <v>28</v>
-      </c>
-      <c r="L55" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2126,15 +2125,15 @@
         <v>106</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="C56" t="s">
         <v>16</v>
       </c>
       <c r="E56" t="s">
-        <v>28</v>
-      </c>
-      <c r="L56" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2143,29 +2142,38 @@
         <v>107</v>
       </c>
       <c r="B57" t="s">
-        <v>108</v>
+        <v>19</v>
       </c>
       <c r="C57" t="s">
         <v>16</v>
       </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
       <c r="E57" t="s">
         <v>17</v>
+      </c>
+      <c r="J57" t="s">
+        <v>20</v>
+      </c>
+      <c r="M57" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>108</v>
+      </c>
+      <c r="B58" t="s">
         <v>109</v>
       </c>
-      <c r="B58" t="s">
-        <v>110</v>
-      </c>
       <c r="C58" t="s">
         <v>16</v>
       </c>
       <c r="E58" t="s">
         <v>17</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58" t="s">
         <v>20</v>
       </c>
       <c r="N58" t="s">
@@ -2174,209 +2182,203 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B59" t="s">
-        <v>110</v>
-      </c>
-      <c r="C59" t="s">
-        <v>16</v>
-      </c>
-      <c r="E59" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+      <c r="B60" t="s">
+        <v>38</v>
+      </c>
+      <c r="C60" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" t="s">
+        <v>28</v>
+      </c>
+      <c r="N60" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A61" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B60" t="s">
-        <v>113</v>
-      </c>
-      <c r="C60" t="s">
-        <v>16</v>
-      </c>
-      <c r="D60" t="s">
-        <v>13</v>
-      </c>
-      <c r="E60" t="s">
-        <v>17</v>
-      </c>
-      <c r="L60" t="s">
-        <v>20</v>
-      </c>
-      <c r="N60" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>114</v>
-      </c>
       <c r="B61" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E61" t="s">
-        <v>17</v>
-      </c>
-      <c r="P61" t="s">
+        <v>28</v>
+      </c>
+      <c r="J61" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C62" t="s">
         <v>16</v>
       </c>
       <c r="E62" t="s">
-        <v>17</v>
-      </c>
-      <c r="K62" t="s">
+        <v>28</v>
+      </c>
+      <c r="J62" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B63" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>115</v>
       </c>
       <c r="E63" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" t="s">
+        <v>28</v>
+      </c>
+      <c r="I63" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>116</v>
+      </c>
+      <c r="B64" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" t="s">
+        <v>16</v>
+      </c>
+      <c r="D64" t="s">
+        <v>146</v>
+      </c>
+      <c r="E64" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" t="s">
+        <v>20</v>
+      </c>
+      <c r="P64" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>117</v>
       </c>
-      <c r="B64" t="s">
-        <v>19</v>
-      </c>
-      <c r="C64" t="s">
-        <v>16</v>
-      </c>
-      <c r="D64" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" t="s">
-        <v>20</v>
-      </c>
-      <c r="M64" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" t="s">
+        <v>115</v>
+      </c>
+      <c r="E65" t="s">
+        <v>28</v>
+      </c>
+      <c r="I65" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>118</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B66" t="s">
         <v>119</v>
       </c>
-      <c r="C65" t="s">
-        <v>16</v>
-      </c>
-      <c r="E65" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" t="s">
-        <v>20</v>
-      </c>
-      <c r="N65" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+      <c r="C66" t="s">
+        <v>127</v>
+      </c>
+      <c r="E66" t="s">
+        <v>28</v>
+      </c>
+      <c r="I66" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>120</v>
       </c>
-      <c r="B66" t="s">
-        <v>90</v>
-      </c>
-      <c r="C66" t="s">
-        <v>16</v>
-      </c>
-      <c r="E66" t="s">
-        <v>17</v>
-      </c>
-      <c r="G66" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A67" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="B67" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="C67" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="E67" t="s">
         <v>28</v>
       </c>
-      <c r="N67" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A68" s="3" t="s">
-        <v>122</v>
+      <c r="I67" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>121</v>
       </c>
       <c r="B68" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="C68" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E68" t="s">
         <v>28</v>
       </c>
-      <c r="J68" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="I68" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B69" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C69" t="s">
         <v>16</v>
       </c>
       <c r="E69" t="s">
-        <v>28</v>
-      </c>
-      <c r="J69" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="I69" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B70" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="C70" t="s">
         <v>16</v>
@@ -2384,90 +2386,93 @@
       <c r="E70" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="H70" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="B71" t="s">
         <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>126</v>
+        <v>16</v>
       </c>
       <c r="E71" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>129</v>
+      </c>
+      <c r="B72" t="s">
+        <v>144</v>
+      </c>
+      <c r="C72" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" t="s">
         <v>28</v>
       </c>
-      <c r="I71" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>127</v>
-      </c>
-      <c r="B72" t="s">
-        <v>41</v>
-      </c>
-      <c r="C72" t="s">
-        <v>16</v>
-      </c>
-      <c r="D72" t="s">
-        <v>158</v>
-      </c>
-      <c r="E72" t="s">
-        <v>17</v>
-      </c>
-      <c r="I72" t="s">
-        <v>20</v>
-      </c>
-      <c r="P72" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K72" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="C73" t="s">
-        <v>126</v>
+        <v>16</v>
+      </c>
+      <c r="D73" t="s">
+        <v>10</v>
       </c>
       <c r="E73" t="s">
         <v>28</v>
       </c>
-      <c r="I73" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K73" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B74" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="C74" t="s">
-        <v>138</v>
+        <v>16</v>
+      </c>
+      <c r="D74" t="s">
+        <v>10</v>
       </c>
       <c r="E74" t="s">
         <v>28</v>
       </c>
-      <c r="I74" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="K74" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B75" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="E75" t="s">
         <v>28</v>
@@ -2476,194 +2481,188 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B76" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C76" t="s">
         <v>16</v>
       </c>
+      <c r="D76" t="s">
+        <v>160</v>
+      </c>
       <c r="E76" t="s">
-        <v>28</v>
-      </c>
-      <c r="I76" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="O76" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B77" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="C77" t="s">
         <v>16</v>
       </c>
+      <c r="D77" t="s">
+        <v>160</v>
+      </c>
       <c r="E77" t="s">
         <v>17</v>
       </c>
-      <c r="I77" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O77" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B78" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
         <v>16</v>
       </c>
       <c r="E78" t="s">
-        <v>28</v>
-      </c>
-      <c r="H78" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+      <c r="O78" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="B79" t="s">
+        <v>161</v>
+      </c>
+      <c r="C79" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" t="s">
+        <v>17</v>
+      </c>
+      <c r="O79" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>139</v>
+      </c>
+      <c r="B80" t="s">
         <v>26</v>
       </c>
-      <c r="C79" t="s">
-        <v>16</v>
-      </c>
-      <c r="E79" t="s">
-        <v>17</v>
-      </c>
-      <c r="I79" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
+      <c r="C80" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80" t="s">
+        <v>17</v>
+      </c>
+      <c r="O80" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>195</v>
+      </c>
+      <c r="B81" t="s">
         <v>140</v>
       </c>
-      <c r="B80" t="s">
-        <v>156</v>
-      </c>
-      <c r="C80" t="s">
-        <v>16</v>
-      </c>
-      <c r="E80" t="s">
-        <v>28</v>
-      </c>
-      <c r="K80" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+      <c r="C81" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" t="s">
+        <v>17</v>
+      </c>
+      <c r="O81" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>141</v>
+      </c>
+      <c r="B82" t="s">
+        <v>126</v>
+      </c>
+      <c r="C82" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82" t="s">
+        <v>17</v>
+      </c>
+      <c r="O82" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>142</v>
       </c>
-      <c r="B81" t="s">
-        <v>84</v>
-      </c>
-      <c r="C81" t="s">
-        <v>16</v>
-      </c>
-      <c r="D81" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" t="s">
-        <v>28</v>
-      </c>
-      <c r="K81" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="B83" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" t="s">
+        <v>17</v>
+      </c>
+      <c r="O83" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>143</v>
       </c>
-      <c r="B82" t="s">
-        <v>72</v>
-      </c>
-      <c r="C82" t="s">
-        <v>16</v>
-      </c>
-      <c r="D82" t="s">
-        <v>10</v>
-      </c>
-      <c r="E82" t="s">
-        <v>28</v>
-      </c>
-      <c r="K82" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="B84" t="s">
         <v>144</v>
       </c>
-      <c r="B83" t="s">
-        <v>26</v>
-      </c>
-      <c r="C83" t="s">
-        <v>126</v>
-      </c>
-      <c r="E83" t="s">
-        <v>28</v>
-      </c>
-      <c r="I83" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>147</v>
-      </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
+        <v>16</v>
+      </c>
+      <c r="E84" t="s">
+        <v>17</v>
+      </c>
+      <c r="O84" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>145</v>
+      </c>
+      <c r="B85" t="s">
+        <v>66</v>
+      </c>
+      <c r="C85" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85" t="s">
+        <v>17</v>
+      </c>
+      <c r="O85" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>148</v>
       </c>
-      <c r="C84" t="s">
-        <v>16</v>
-      </c>
-      <c r="D84" t="s">
-        <v>173</v>
-      </c>
-      <c r="E84" t="s">
-        <v>17</v>
-      </c>
-      <c r="O84" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>146</v>
-      </c>
-      <c r="B85" t="s">
-        <v>24</v>
-      </c>
-      <c r="C85" t="s">
-        <v>16</v>
-      </c>
-      <c r="D85" t="s">
-        <v>173</v>
-      </c>
-      <c r="E85" t="s">
-        <v>17</v>
-      </c>
-      <c r="O85" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>145</v>
-      </c>
       <c r="B86" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C86" t="s">
         <v>16</v>
@@ -2675,233 +2674,233 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>149</v>
       </c>
       <c r="B87" t="s">
+        <v>150</v>
+      </c>
+      <c r="C87" t="s">
+        <v>16</v>
+      </c>
+      <c r="E87" t="s">
+        <v>17</v>
+      </c>
+      <c r="O87" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>154</v>
+      </c>
+      <c r="B88" t="s">
+        <v>155</v>
+      </c>
+      <c r="C88" t="s">
+        <v>16</v>
+      </c>
+      <c r="E88" t="s">
+        <v>17</v>
+      </c>
+      <c r="O88" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>156</v>
+      </c>
+      <c r="B89" t="s">
+        <v>157</v>
+      </c>
+      <c r="C89" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" t="s">
+        <v>17</v>
+      </c>
+      <c r="O89" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>158</v>
+      </c>
+      <c r="B90" t="s">
+        <v>159</v>
+      </c>
+      <c r="C90" t="s">
+        <v>16</v>
+      </c>
+      <c r="E90" t="s">
+        <v>17</v>
+      </c>
+      <c r="O90" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>162</v>
+      </c>
+      <c r="B91" t="s">
+        <v>163</v>
+      </c>
+      <c r="C91" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" t="s">
+        <v>17</v>
+      </c>
+      <c r="O91" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>164</v>
+      </c>
+      <c r="B92" t="s">
+        <v>41</v>
+      </c>
+      <c r="C92" t="s">
+        <v>16</v>
+      </c>
+      <c r="E92" t="s">
+        <v>17</v>
+      </c>
+      <c r="O92" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>151</v>
+      </c>
+      <c r="B93" t="s">
+        <v>130</v>
+      </c>
+      <c r="C93" t="s">
+        <v>16</v>
+      </c>
+      <c r="E93" t="s">
+        <v>17</v>
+      </c>
+      <c r="K93" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>165</v>
+      </c>
+      <c r="B94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" t="s">
+        <v>28</v>
+      </c>
+      <c r="J94" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A95" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C95" t="s">
+        <v>16</v>
+      </c>
+      <c r="E95" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A96" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B96" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A97" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B97" t="s">
+        <v>57</v>
+      </c>
+      <c r="C97" t="s">
+        <v>16</v>
+      </c>
+      <c r="E97" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A98" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C98" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A99" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C87" t="s">
-        <v>16</v>
-      </c>
-      <c r="E87" t="s">
-        <v>17</v>
-      </c>
-      <c r="O87" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>150</v>
-      </c>
-      <c r="B88" t="s">
-        <v>26</v>
-      </c>
-      <c r="C88" t="s">
-        <v>16</v>
-      </c>
-      <c r="E88" t="s">
-        <v>17</v>
-      </c>
-      <c r="O88" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>151</v>
-      </c>
-      <c r="B89" t="s">
-        <v>152</v>
-      </c>
-      <c r="C89" t="s">
-        <v>16</v>
-      </c>
-      <c r="E89" t="s">
-        <v>17</v>
-      </c>
-      <c r="O89" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>153</v>
-      </c>
-      <c r="B90" t="s">
+      <c r="B99" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C90" t="s">
-        <v>16</v>
-      </c>
-      <c r="E90" t="s">
-        <v>17</v>
-      </c>
-      <c r="O90" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>154</v>
-      </c>
-      <c r="B91" t="s">
-        <v>62</v>
-      </c>
-      <c r="C91" t="s">
-        <v>16</v>
-      </c>
-      <c r="E91" t="s">
-        <v>17</v>
-      </c>
-      <c r="O91" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>155</v>
-      </c>
-      <c r="B92" t="s">
-        <v>156</v>
-      </c>
-      <c r="C92" t="s">
-        <v>16</v>
-      </c>
-      <c r="E92" t="s">
-        <v>17</v>
-      </c>
-      <c r="O92" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>157</v>
-      </c>
-      <c r="B93" t="s">
-        <v>72</v>
-      </c>
-      <c r="C93" t="s">
-        <v>16</v>
-      </c>
-      <c r="E93" t="s">
-        <v>17</v>
-      </c>
-      <c r="O93" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>160</v>
-      </c>
-      <c r="B94" t="s">
-        <v>81</v>
-      </c>
-      <c r="C94" t="s">
-        <v>16</v>
-      </c>
-      <c r="E94" t="s">
-        <v>17</v>
-      </c>
-      <c r="O94" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>161</v>
-      </c>
-      <c r="B95" t="s">
-        <v>162</v>
-      </c>
-      <c r="C95" t="s">
-        <v>16</v>
-      </c>
-      <c r="E95" t="s">
-        <v>17</v>
-      </c>
-      <c r="O95" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>167</v>
-      </c>
-      <c r="B96" t="s">
-        <v>168</v>
-      </c>
-      <c r="C96" t="s">
-        <v>16</v>
-      </c>
-      <c r="E96" t="s">
-        <v>17</v>
-      </c>
-      <c r="O96" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>169</v>
-      </c>
-      <c r="B97" t="s">
-        <v>170</v>
-      </c>
-      <c r="C97" t="s">
-        <v>16</v>
-      </c>
-      <c r="E97" t="s">
-        <v>17</v>
-      </c>
-      <c r="O97" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>171</v>
-      </c>
-      <c r="B98" t="s">
-        <v>172</v>
-      </c>
-      <c r="C98" t="s">
-        <v>16</v>
-      </c>
-      <c r="E98" t="s">
-        <v>17</v>
-      </c>
-      <c r="O98" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>175</v>
-      </c>
-      <c r="B99" t="s">
-        <v>176</v>
-      </c>
       <c r="C99" t="s">
         <v>16</v>
       </c>
       <c r="E99" t="s">
         <v>17</v>
       </c>
-      <c r="O99" t="s">
+      <c r="Q99" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B100" t="s">
-        <v>41</v>
+        <v>130</v>
       </c>
       <c r="C100" t="s">
         <v>16</v>
@@ -2909,33 +2908,33 @@
       <c r="E100" t="s">
         <v>17</v>
       </c>
-      <c r="O100" t="s">
+      <c r="Q100" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B101" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="C101" t="s">
         <v>16</v>
       </c>
       <c r="E101" t="s">
-        <v>28</v>
-      </c>
-      <c r="P101" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q101" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B102" t="s">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="C102" t="s">
         <v>16</v>
@@ -2943,7 +2942,7 @@
       <c r="E102" t="s">
         <v>17</v>
       </c>
-      <c r="K102" t="s">
+      <c r="Q102" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2952,23 +2951,26 @@
         <v>178</v>
       </c>
       <c r="B103" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="C103" t="s">
         <v>16</v>
       </c>
+      <c r="D103" t="s">
+        <v>168</v>
+      </c>
       <c r="E103" t="s">
-        <v>28</v>
-      </c>
-      <c r="J103" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q103" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A104" s="5" t="s">
+      <c r="A104" t="s">
         <v>179</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" t="s">
         <v>180</v>
       </c>
       <c r="C104" t="s">
@@ -2982,62 +2984,62 @@
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A105" s="5" t="s">
+      <c r="A105" t="s">
+        <v>181</v>
+      </c>
+      <c r="B105" t="s">
+        <v>137</v>
+      </c>
+      <c r="C105" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A106" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B106" t="s">
+        <v>161</v>
+      </c>
+      <c r="C106" t="s">
+        <v>16</v>
+      </c>
+      <c r="E106" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A107" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C105" t="s">
-        <v>16</v>
-      </c>
-      <c r="E105" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q105" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A106" s="5" t="s">
+      <c r="B107" t="s">
         <v>184</v>
       </c>
-      <c r="B106" t="s">
-        <v>62</v>
-      </c>
-      <c r="C106" t="s">
-        <v>16</v>
-      </c>
-      <c r="E106" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q106" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A107" s="5" t="s">
+      <c r="C107" t="s">
+        <v>16</v>
+      </c>
+      <c r="E107" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
         <v>185</v>
       </c>
-      <c r="B107" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C107" t="s">
-        <v>16</v>
-      </c>
-      <c r="E107" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q107" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A108" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>148</v>
+      <c r="B108" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
@@ -3051,10 +3053,10 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>188</v>
-      </c>
-      <c r="B109" t="s">
-        <v>141</v>
+        <v>186</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
@@ -3067,8 +3069,8 @@
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A110" t="s">
-        <v>189</v>
+      <c r="A110" s="4" t="s">
+        <v>187</v>
       </c>
       <c r="B110" t="s">
         <v>24</v>
@@ -3084,95 +3086,92 @@
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+      <c r="A111" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C111" t="s">
+        <v>16</v>
+      </c>
+      <c r="E111" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A112" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B111" t="s">
-        <v>41</v>
-      </c>
-      <c r="C111" t="s">
-        <v>16</v>
-      </c>
-      <c r="E111" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q111" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+      <c r="B112" t="s">
+        <v>75</v>
+      </c>
+      <c r="C112" t="s">
+        <v>16</v>
+      </c>
+      <c r="E112" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A113" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B112" t="s">
-        <v>81</v>
-      </c>
-      <c r="C112" t="s">
-        <v>16</v>
-      </c>
-      <c r="D112" t="s">
-        <v>181</v>
-      </c>
-      <c r="E112" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A113" t="s">
+      <c r="B113" t="s">
         <v>192</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
+        <v>16</v>
+      </c>
+      <c r="E113" t="s">
+        <v>28</v>
+      </c>
+      <c r="K113" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A114" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C113" t="s">
-        <v>16</v>
-      </c>
-      <c r="E113" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A114" t="s">
+      <c r="B114" t="s">
+        <v>19</v>
+      </c>
+      <c r="C114" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" t="s">
+        <v>28</v>
+      </c>
+      <c r="K114" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A115" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B114" t="s">
-        <v>148</v>
-      </c>
-      <c r="C114" t="s">
-        <v>16</v>
-      </c>
-      <c r="E114" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A115" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="B115" t="s">
-        <v>174</v>
+        <v>137</v>
       </c>
       <c r="C115" t="s">
         <v>16</v>
       </c>
       <c r="E115" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q115" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A116" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K115" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
         <v>196</v>
       </c>
       <c r="B116" t="s">
@@ -3184,16 +3183,16 @@
       <c r="E116" t="s">
         <v>17</v>
       </c>
-      <c r="Q116" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O116" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>198</v>
       </c>
-      <c r="B117" s="5" t="s">
-        <v>180</v>
+      <c r="B117" t="s">
+        <v>197</v>
       </c>
       <c r="C117" t="s">
         <v>16</v>
@@ -3201,141 +3200,56 @@
       <c r="E117" t="s">
         <v>17</v>
       </c>
-      <c r="Q117" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="O117" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>199</v>
       </c>
-      <c r="B118" s="5" t="s">
-        <v>19</v>
+      <c r="B118" t="s">
+        <v>26</v>
       </c>
       <c r="C118" t="s">
         <v>16</v>
       </c>
       <c r="E118" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q118" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A119" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="P118" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
         <v>200</v>
       </c>
       <c r="B119" t="s">
-        <v>24</v>
+        <v>201</v>
       </c>
       <c r="C119" t="s">
         <v>16</v>
       </c>
       <c r="E119" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q119" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A120" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C120" t="s">
-        <v>16</v>
-      </c>
-      <c r="E120" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q120" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A121" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B121" t="s">
-        <v>81</v>
-      </c>
-      <c r="C121" t="s">
-        <v>16</v>
-      </c>
-      <c r="E121" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q121" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A122" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B122" t="s">
-        <v>205</v>
-      </c>
-      <c r="C122" t="s">
-        <v>16</v>
-      </c>
-      <c r="E122" t="s">
         <v>28</v>
       </c>
-      <c r="K122" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A123" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B123" t="s">
-        <v>19</v>
-      </c>
-      <c r="C123" t="s">
-        <v>16</v>
-      </c>
-      <c r="E123" t="s">
-        <v>28</v>
-      </c>
-      <c r="K123" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A124" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B124" t="s">
-        <v>148</v>
-      </c>
-      <c r="C124" t="s">
-        <v>16</v>
-      </c>
-      <c r="E124" t="s">
-        <v>28</v>
-      </c>
-      <c r="K124" t="s">
+      <c r="P119" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A59" r:id="rId1" display="mailto:Katsumi.Yoshida@ucb.com" xr:uid="{AD08391F-3F27-4BAB-B3CA-FAD4219C74FB}"/>
-    <hyperlink ref="A31" r:id="rId2" display="mailto:Armin.Schueler@merckgroup.com" xr:uid="{FB4A5F2A-36D0-43FF-8E86-BC1FDA6D1D6D}"/>
-    <hyperlink ref="A46" r:id="rId3" display="mailto:Sue.McKendrick@ppdi.com" xr:uid="{DE8DF6B5-533F-4E12-B663-0DC5B3468A5B}"/>
-    <hyperlink ref="A57" r:id="rId4" display="mailto:estelle.lambert@servier.com" xr:uid="{651C634A-99D2-42A8-BB08-FD8205D37AC1}"/>
-    <hyperlink ref="A13" r:id="rId5" display="mailto:Lorenzo.Guizzaro@ema.europa.eu" xr:uid="{C2849AD9-061A-49AD-9B46-1F76360B127A}"/>
-    <hyperlink ref="A21" r:id="rId6" display="mailto:oliverkeene405@gmail.com" xr:uid="{20FEF294-7B67-4A68-9F37-488C17101DEC}"/>
-    <hyperlink ref="A11" r:id="rId7" display="mailto:s.vezzoli@chiesi.com" xr:uid="{59FACA81-FC0A-48B9-9BBF-5AA75FA20B6C}"/>
-    <hyperlink ref="A20" r:id="rId8" display="mailto:carrie.li@idorsia.com" xr:uid="{324A16D9-7045-4977-92A4-5CD67D6BD979}"/>
-    <hyperlink ref="A64" r:id="rId9" display="mailto:chun-hang.x.tang@gsk.com" xr:uid="{C442D243-F2D4-4809-9C20-7E0E35C1AC02}"/>
-    <hyperlink ref="A97" r:id="rId10" display="mailto:jianjun.x.gan@viivhealthcare.com" xr:uid="{E8FCEFA5-0BC1-4855-AE3E-225FED9844AA}"/>
+    <hyperlink ref="A52" r:id="rId1" display="mailto:Katsumi.Yoshida@ucb.com" xr:uid="{801335CD-73CB-4DB9-8491-F13BA3F36A4C}"/>
+    <hyperlink ref="A28" r:id="rId2" display="mailto:Armin.Schueler@merckgroup.com" xr:uid="{F09E2010-4B29-473E-8484-4A91F07BD642}"/>
+    <hyperlink ref="A43" r:id="rId3" display="mailto:Sue.McKendrick@ppdi.com" xr:uid="{7CC60960-DA80-4E07-98A3-AB2869AFE059}"/>
+    <hyperlink ref="A50" r:id="rId4" display="mailto:estelle.lambert@servier.com" xr:uid="{9517C175-943F-4DF4-9A20-29EC27A26B7F}"/>
+    <hyperlink ref="A13" r:id="rId5" display="mailto:Lorenzo.Guizzaro@ema.europa.eu" xr:uid="{FEE2611A-0FEF-4EFD-B9F2-75D7C5B252B1}"/>
+    <hyperlink ref="A21" r:id="rId6" display="mailto:oliverkeene405@gmail.com" xr:uid="{FC4AE0DE-485D-41EC-9147-2EFAF3D783B2}"/>
+    <hyperlink ref="A11" r:id="rId7" display="mailto:s.vezzoli@chiesi.com" xr:uid="{232510D9-F755-4F38-9525-9A77E3348682}"/>
+    <hyperlink ref="A20" r:id="rId8" display="mailto:carrie.li@idorsia.com" xr:uid="{221BE687-050A-4A8C-8393-CB76F897AA8B}"/>
+    <hyperlink ref="A57" r:id="rId9" display="mailto:chun-hang.x.tang@gsk.com" xr:uid="{501F9104-19BE-4F3B-931A-C497D6A431E1}"/>
+    <hyperlink ref="A89" r:id="rId10" display="mailto:jianjun.x.gan@viivhealthcare.com" xr:uid="{5815AC86-055F-44F9-9BAA-0F95E266EAAF}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="61" fitToHeight="0" orientation="landscape" r:id="rId11"/>
@@ -3346,18 +3260,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3505,18 +3419,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5478ECA-E19E-4E78-97DE-7171B34BD30F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1288C358-E90E-46A5-8B49-D40D5385BECC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1288C358-E90E-46A5-8B49-D40D5385BECC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5478ECA-E19E-4E78-97DE-7171B34BD30F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e85c81c27d35d093/Dokumente/Webseiten/EIWG/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{D1314935-C5B3-4AE7-B730-4C7C0C7E3407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAD0DFA5-AE32-4D73-90F0-1E3589E25781}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{D1314935-C5B3-4AE7-B730-4C7C0C7E3407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB975605-0DFA-428B-B53A-4B6780B23551}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1233,7 +1233,7 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="C6" t="s">
         <v>16</v>
@@ -3240,16 +3240,16 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A52" r:id="rId1" display="mailto:Katsumi.Yoshida@ucb.com" xr:uid="{801335CD-73CB-4DB9-8491-F13BA3F36A4C}"/>
-    <hyperlink ref="A28" r:id="rId2" display="mailto:Armin.Schueler@merckgroup.com" xr:uid="{F09E2010-4B29-473E-8484-4A91F07BD642}"/>
-    <hyperlink ref="A43" r:id="rId3" display="mailto:Sue.McKendrick@ppdi.com" xr:uid="{7CC60960-DA80-4E07-98A3-AB2869AFE059}"/>
-    <hyperlink ref="A50" r:id="rId4" display="mailto:estelle.lambert@servier.com" xr:uid="{9517C175-943F-4DF4-9A20-29EC27A26B7F}"/>
-    <hyperlink ref="A13" r:id="rId5" display="mailto:Lorenzo.Guizzaro@ema.europa.eu" xr:uid="{FEE2611A-0FEF-4EFD-B9F2-75D7C5B252B1}"/>
-    <hyperlink ref="A21" r:id="rId6" display="mailto:oliverkeene405@gmail.com" xr:uid="{FC4AE0DE-485D-41EC-9147-2EFAF3D783B2}"/>
-    <hyperlink ref="A11" r:id="rId7" display="mailto:s.vezzoli@chiesi.com" xr:uid="{232510D9-F755-4F38-9525-9A77E3348682}"/>
-    <hyperlink ref="A20" r:id="rId8" display="mailto:carrie.li@idorsia.com" xr:uid="{221BE687-050A-4A8C-8393-CB76F897AA8B}"/>
-    <hyperlink ref="A57" r:id="rId9" display="mailto:chun-hang.x.tang@gsk.com" xr:uid="{501F9104-19BE-4F3B-931A-C497D6A431E1}"/>
-    <hyperlink ref="A89" r:id="rId10" display="mailto:jianjun.x.gan@viivhealthcare.com" xr:uid="{5815AC86-055F-44F9-9BAA-0F95E266EAAF}"/>
+    <hyperlink ref="A52" r:id="rId1" display="mailto:Katsumi.Yoshida@ucb.com" xr:uid="{79BC1F46-006E-4EC2-B463-90C3B8752E0F}"/>
+    <hyperlink ref="A28" r:id="rId2" display="mailto:Armin.Schueler@merckgroup.com" xr:uid="{54A966E2-B202-49AB-A815-C3E7EB9A7F1B}"/>
+    <hyperlink ref="A43" r:id="rId3" display="mailto:Sue.McKendrick@ppdi.com" xr:uid="{3F6B1EC0-6E02-4854-8DEB-7BDFD6A394FB}"/>
+    <hyperlink ref="A50" r:id="rId4" display="mailto:estelle.lambert@servier.com" xr:uid="{2817B567-9CE5-4BA2-B4E4-40BA79143115}"/>
+    <hyperlink ref="A13" r:id="rId5" display="mailto:Lorenzo.Guizzaro@ema.europa.eu" xr:uid="{0FAA227A-5815-4717-B7DE-8FF2EBF4D65C}"/>
+    <hyperlink ref="A21" r:id="rId6" display="mailto:oliverkeene405@gmail.com" xr:uid="{4593E44C-B30A-415E-816F-4D1462850A1C}"/>
+    <hyperlink ref="A11" r:id="rId7" display="mailto:s.vezzoli@chiesi.com" xr:uid="{899E8E4B-6C18-4862-AD50-DCBD3B649E4B}"/>
+    <hyperlink ref="A20" r:id="rId8" display="mailto:carrie.li@idorsia.com" xr:uid="{CAE708B3-2294-4024-A52A-9110B957A0AE}"/>
+    <hyperlink ref="A57" r:id="rId9" display="mailto:chun-hang.x.tang@gsk.com" xr:uid="{29A84DA7-FC4F-48BE-B58A-06EDC9649DAF}"/>
+    <hyperlink ref="A89" r:id="rId10" display="mailto:jianjun.x.gan@viivhealthcare.com" xr:uid="{BCA09DEA-DDA2-46A1-B92F-581A9DD3D755}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="61" fitToHeight="0" orientation="landscape" r:id="rId11"/>
@@ -3260,21 +3260,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100C2547C8CC7B331428FF953FE0CD11F32" ma:contentTypeVersion="4" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="21585f8105577c55a14177137b0f487c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fe6cebb0-ac24-4097-a45b-aec9fe749aaa" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a739419b1432b2a493df12220e235f53" ns2:_="">
     <xsd:import namespace="fe6cebb0-ac24-4097-a45b-aec9fe749aaa"/>
@@ -3418,24 +3403,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1288C358-E90E-46A5-8B49-D40D5385BECC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5478ECA-E19E-4E78-97DE-7171B34BD30F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E44DC42-D40D-4161-B416-680814B33C76}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3451,4 +3434,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5478ECA-E19E-4E78-97DE-7171B34BD30F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1288C358-E90E-46A5-8B49-D40D5385BECC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>